--- a/outputs/patched_all_results.xlsx
+++ b/outputs/patched_all_results.xlsx
@@ -463,1057 +463,1057 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": -1, "learning_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.38311106605815</v>
+        <v>7.008227184414864</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8382990760775433</v>
+        <v>1.806422563115009</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8399360434569649</v>
+        <v>-0.2156415700912476</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1572152092282791</v>
+        <v>1.880556148377381</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 10, "learning_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.38311106605815</v>
+        <v>7.337846234440804</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8382990760775433</v>
+        <v>1.245960502015729</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8399360434569649</v>
+        <v>-0.131558883190155</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1572152092282791</v>
+        <v>1.67337335093499</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 10, "learning_rate": 0.05}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.443458120526798</v>
+        <v>7.354888394474983</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7814284156648358</v>
+        <v>1.241677961305935</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8447132290765742</v>
+        <v>-0.2867695450782776</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1508930253408941</v>
+        <v>2.033857286620624</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": -1, "learning_rate": 0.05}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.443458120526798</v>
+        <v>7.399432957172394</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7814284156648358</v>
+        <v>1.002939627174502</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8447132290765742</v>
+        <v>-0.3637040734291077</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1508930253408941</v>
+        <v>2.157002349434029</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 10, "learning_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.450704347626784</v>
+        <v>7.512368187308311</v>
       </c>
       <c r="D6" t="n">
-        <v>0.787863497077703</v>
+        <v>1.645555578754827</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8426613838998603</v>
+        <v>-0.3288786888122558</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1527128062285151</v>
+        <v>2.076853088045143</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": -1, "learning_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.450704347626784</v>
+        <v>7.526438385248184</v>
       </c>
       <c r="D7" t="n">
-        <v>0.787863497077703</v>
+        <v>0.9080439666835051</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8426613838998603</v>
+        <v>-0.3799163341522217</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1527128062285151</v>
+        <v>2.179657940272019</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": -1, "learning_rate": 0.05}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.460939677865788</v>
+        <v>7.588866129517555</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7286796510001985</v>
+        <v>2.38422628248335</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8475320055619221</v>
+        <v>-0.1601909637451172</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1443666449819211</v>
+        <v>1.702204598454322</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 10, "learning_rate": 0.05}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.460939677865788</v>
+        <v>7.686254307627678</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7286796510001985</v>
+        <v>1.665289206544194</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8475320055619221</v>
+        <v>-0.2653233528137207</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1443666449819211</v>
+        <v>1.914745098252183</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": -1, "learning_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.50915591049173</v>
+        <v>7.715515419840813</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7216910597982266</v>
+        <v>2.016977309233021</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8464024927447887</v>
+        <v>-0.3624902844429016</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1438853612379712</v>
+        <v>2.1171832357687</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 10, "learning_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4.50915591049173</v>
+        <v>7.734411805868149</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7216910597982266</v>
+        <v>1.830864770104565</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8464024927447887</v>
+        <v>-0.7732484936714172</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1438853612379712</v>
+        <v>2.961306847957459</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.05}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.513185136020184</v>
+        <v>7.78913751244545</v>
       </c>
       <c r="D12" t="n">
-        <v>1.185848316009084</v>
+        <v>2.292925555719514</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8446412205696106</v>
+        <v>-0.2554660558700562</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1423042298478086</v>
+        <v>1.871534421592341</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.05}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.515276957380676</v>
+        <v>7.821034267544746</v>
       </c>
       <c r="D13" t="n">
-        <v>1.100575854605122</v>
+        <v>1.917115592613151</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8452314358190025</v>
+        <v>-1.213700890541077</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1417561775597533</v>
+        <v>3.87492543276828</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.549439400434494</v>
+        <v>7.84952200949192</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9723089042291687</v>
+        <v>1.463320145213179</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8421426296234131</v>
+        <v>-0.9677449584007263</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1443667727216928</v>
+        <v>3.339907790674223</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.05}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.574780687689781</v>
+        <v>7.865811958909035</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9983827984968147</v>
+        <v>1.95313843414171</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8380012154579163</v>
+        <v>-0.3300805687904358</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1510377325654267</v>
+        <v>2.031926531673224</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 3, "learning_rate": 0.05}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.680777415633202</v>
+        <v>7.879435569047928</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8376868267760426</v>
+        <v>2.172896935367853</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8371237754821778</v>
+        <v>-0.220680820941925</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1527222969939294</v>
+        <v>1.75192636251522</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 100.0, "epsilon": 0.5, "gamma": "scale"}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.680995325390169</v>
+        <v>7.907520532608032</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6590121096294085</v>
+        <v>2.374089320502033</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8159191516526692</v>
+        <v>-0.255685293674469</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1848191467394336</v>
+        <v>1.845304244250106</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.05}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4.688526481985832</v>
+        <v>7.984851002693176</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9169153648042024</v>
+        <v>2.687602635802328</v>
       </c>
       <c r="E18" t="n">
-        <v>0.840207373872612</v>
+        <v>-0.2799176096916199</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1441226012028219</v>
+        <v>1.934921594513607</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.694216884092149</v>
+        <v>8.037720769643784</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8840527855312751</v>
+        <v>1.760985233441941</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8415040335453996</v>
+        <v>-0.2800532817840576</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1427540446518229</v>
+        <v>1.882080652993529</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 20, "min_samples_split": 5}</t>
+          <t>{"n_estimators": 100, "max_depth": 6, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.695641247601482</v>
+        <v>8.101582489907742</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8554419330055419</v>
+        <v>3.210604968300438</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8371018538266615</v>
+        <v>-0.8935428142547608</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1482500276022976</v>
+        <v>3.107819528469434</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": null, "min_samples_split": 5}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.695641247601483</v>
+        <v>8.144230246543884</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8554419330055418</v>
+        <v>1.992813032722124</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8371018538266615</v>
+        <v>-0.8433944702148437</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1482500276022975</v>
+        <v>3.023354827802414</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 10, "min_samples_split": 5}</t>
+          <t>{"n_estimators": 300, "max_depth": 6, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.695641247601483</v>
+        <v>8.147105649113655</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8554419330055434</v>
+        <v>3.094712065239836</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8371018538266615</v>
+        <v>-0.9042950749397278</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1482500276022977</v>
+        <v>3.113335835277763</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 10, "min_samples_split": 5}</t>
+          <t>{"n_estimators": 200, "max_depth": 6, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4.696043172076537</v>
+        <v>8.147107735276222</v>
       </c>
       <c r="D23" t="n">
-        <v>0.829264663129011</v>
+        <v>3.094713724093713</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8378920145653108</v>
+        <v>-0.9042957425117493</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1465243009906089</v>
+        <v>3.113335570210114</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": null, "min_samples_split": 5}</t>
+          <t>{"n_estimators": 100, "max_depth": 6, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.696043172076539</v>
+        <v>8.153611570596695</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8292646631290104</v>
+        <v>3.100009743201206</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8378920145653108</v>
+        <v>-0.9036031723022461</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1465243009906087</v>
+        <v>3.111199033611178</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 20, "min_samples_split": 5}</t>
+          <t>{"n_estimators": 200, "max_depth": 6, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.696043172076541</v>
+        <v>8.181932866573334</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8292646631290097</v>
+        <v>3.121981932124025</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8378920145653106</v>
+        <v>-0.902649462223053</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1465243009906089</v>
+        <v>3.108745897750085</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 6, "learning_rate": 0.05}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.696210622787476</v>
+        <v>8.188274726271629</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9715836628400945</v>
+        <v>3.015265801240582</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8338472604751587</v>
+        <v>-0.266542398929596</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1560159832516874</v>
+        <v>1.837251405042614</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 20, "min_samples_split": 5}</t>
+          <t>{"n_estimators": 300, "max_depth": 6, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4.730960810280807</v>
+        <v>8.195406198501587</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8303352062018138</v>
+        <v>3.130318387968636</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8411978423898411</v>
+        <v>-0.9046710968017578</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1378010288674978</v>
+        <v>3.110839165673237</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 10, "min_samples_split": 5}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4.73096081028081</v>
+        <v>8.2733403891325</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8303352062018167</v>
+        <v>2.094498084718726</v>
       </c>
       <c r="E28" t="n">
-        <v>0.841197842389841</v>
+        <v>-0.2409772396087647</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1378010288674978</v>
+        <v>1.772210832294306</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GaussianProcess</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": null, "min_samples_split": 5}</t>
+          <t>{"length_scale": 1.0, "noise": 0.1, "alpha": 1e-06}</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4.73096081028081</v>
+        <v>8.274456265097012</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8303352062018171</v>
+        <v>2.372681136851306</v>
       </c>
       <c r="E29" t="n">
-        <v>0.841197842389841</v>
+        <v>-0.6485867791883132</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1378010288674982</v>
+        <v>2.648537507269835</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>GaussianProcess</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.1}</t>
+          <t>{"length_scale": 1.0, "noise": 1.0, "alpha": 1e-06}</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4.732536002993584</v>
+        <v>8.274508610324212</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8200808456119993</v>
+        <v>2.372700205222115</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8350389719009399</v>
+        <v>-0.6485890803988523</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1549351856420297</v>
+        <v>2.64853632236588</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 10.0, "epsilon": 0.1, "gamma": "scale"}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4.736435495769025</v>
+        <v>8.41796487569809</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7270019177727071</v>
+        <v>1.57396585382823</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8334500817746147</v>
+        <v>-0.6317244648933411</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1315317750309475</v>
+        <v>2.396187824796062</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 100.0, "epsilon": 0.1, "gamma": "scale"}</t>
+          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4.754392413141528</v>
+        <v>8.655803799629211</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7865537613274239</v>
+        <v>2.984180922614528</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7896306378574944</v>
+        <v>-0.6746608018875122</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2321426796487634</v>
+        <v>2.664714483408999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>KAN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": -1, "learning_rate": 0.05}</t>
+          <t>{"width": [16, 1], "grid_size": 5, "spline_order": 3, "learning_rate": 0.01}</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4.755172793542587</v>
+        <v>8.681400418281555</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7839694611141643</v>
+        <v>2.347146236591373</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8444742213599579</v>
+        <v>-0.5991775274276734</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1406443031798408</v>
+        <v>2.47645344682685</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 10, "learning_rate": 0.05}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4.755172793542587</v>
+        <v>8.688124269247055</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7839694611141643</v>
+        <v>1.825866607384403</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8444742213599579</v>
+        <v>-0.7745539665222168</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1406443031798408</v>
+        <v>2.814502995860325</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": null, "min_samples_split": 2}</t>
+          <t>{"n_estimators": 300, "max_depth": 3, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4.774050975789809</v>
+        <v>8.916647732257843</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8700473364346888</v>
+        <v>3.037875230191855</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8396321067827556</v>
+        <v>-0.8289180159568786</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1400898209382298</v>
+        <v>2.927994528575314</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 10, "min_samples_split": 2}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.77405097578981</v>
+        <v>8.933324366807938</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8700473364346877</v>
+        <v>1.378530018468229</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8396321067827557</v>
+        <v>-0.8584981203079224</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1400898209382297</v>
+        <v>2.832614430828353</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 20, "min_samples_split": 2}</t>
+          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4.774050975789811</v>
+        <v>8.940495401620865</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8700473364346875</v>
+        <v>3.007069160676152</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8396321067827557</v>
+        <v>-0.8047483801841736</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1400898209382293</v>
+        <v>2.881341398023585</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": null, "min_samples_split": 2}</t>
+          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.776595734161694</v>
+        <v>8.96710492670536</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8641276000033355</v>
+        <v>3.097149173376365</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8346768715621641</v>
+        <v>-0.8080731630325317</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1515149514089408</v>
+        <v>2.888083486206069</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 20, "min_samples_split": 2}</t>
+          <t>{"n_estimators": 100, "max_depth": 2, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4.776595734161695</v>
+        <v>8.969695066271132</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8641276000033338</v>
+        <v>5.436389452787407</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8346768715621641</v>
+        <v>-0.2023944223499294</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1515149514089408</v>
+        <v>1.638089975486208</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 10, "min_samples_split": 2}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4.776595734161696</v>
+        <v>9.016884565353394</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8641276000033329</v>
+        <v>1.429171107428052</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8346768715621641</v>
+        <v>-0.4446877717971802</v>
       </c>
       <c r="F40" t="n">
-        <v>0.151514951408941</v>
+        <v>2.012007396818917</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 10, "min_samples_split": 2}</t>
+          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4.778063504014069</v>
+        <v>9.017146676778793</v>
       </c>
       <c r="D41" t="n">
-        <v>0.836175810404587</v>
+        <v>3.106684980873905</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8353462650760232</v>
+        <v>-0.8072817206382752</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1501482100634978</v>
+        <v>2.861828240549657</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 20, "min_samples_split": 2}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4.77806350401407</v>
+        <v>9.078070819377899</v>
       </c>
       <c r="D42" t="n">
-        <v>0.836175810404585</v>
+        <v>1.19309542688434</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8353462650760234</v>
+        <v>-0.9348836541175842</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1501482100634979</v>
+        <v>3.072915596729692</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": null, "min_samples_split": 2}</t>
+          <t>{"n_estimators": 300, "max_depth": 3, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4.778063504014071</v>
+        <v>9.120100140571594</v>
       </c>
       <c r="D43" t="n">
-        <v>0.8361758104045868</v>
+        <v>3.165413348554869</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8353462650760232</v>
+        <v>-0.8178203940391541</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1501482100634979</v>
+        <v>2.870053985704804</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.779321646808462</v>
+        <v>9.144393056631088</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8408523487199914</v>
+        <v>1.310089646678104</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8339217800950994</v>
+        <v>-0.5673615097999573</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1557862238979923</v>
+        <v>2.23465232941062</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 3, "learning_rate": 0.1}</t>
+          <t>{"degree": 2, "alpha": 10.0}</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4.802548661828041</v>
+        <v>9.152017384767532</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8071088839858582</v>
+        <v>4.750069616254988</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8326253414154052</v>
+        <v>-0.9252780079841614</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1569701229430916</v>
+        <v>3.142527380882826</v>
       </c>
     </row>
     <row r="46">
@@ -1524,932 +1524,932 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 2, "learning_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": 2, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4.813957779508515</v>
+        <v>9.169641355449674</v>
       </c>
       <c r="D46" t="n">
-        <v>0.8362212047527576</v>
+        <v>4.940937444502639</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8455546496028774</v>
+        <v>-0.3260086735864722</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1347094594351639</v>
+        <v>1.878598819388841</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 2, "learning_rate": 0.1}</t>
+          <t>{"degree": 2, "alpha": 1.0}</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4.818743915086477</v>
+        <v>9.178929105401039</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9941209577726411</v>
+        <v>5.474690467641143</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8460828109034054</v>
+        <v>-0.892299211025238</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1356681881986893</v>
+        <v>3.036484184183736</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{"degree": 3, "alpha": 10.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4.858193770051003</v>
+        <v>9.243708103895187</v>
       </c>
       <c r="D48" t="n">
-        <v>0.8948549917713621</v>
+        <v>1.73074061184955</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8208396434783936</v>
+        <v>-0.4909931302070618</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1590719625245934</v>
+        <v>2.120523371272484</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 6, "learning_rate": 0.05}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4.865444302558899</v>
+        <v>9.417612701654434</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8305038602978101</v>
+        <v>1.255263256561803</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8295156717300415</v>
+        <v>-0.9089695572853088</v>
       </c>
       <c r="F49" t="n">
-        <v>0.157943209104484</v>
+        <v>2.927688385073365</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 6, "learning_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4.866373538970947</v>
+        <v>9.464593380689621</v>
       </c>
       <c r="D50" t="n">
-        <v>0.8281843942169395</v>
+        <v>1.409447727430224</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8294692993164062</v>
+        <v>-1.843887364864349</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1580526891563769</v>
+        <v>4.829143679176703</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 6, "learning_rate": 0.05}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4.871603697538376</v>
+        <v>9.670910239219666</v>
       </c>
       <c r="D51" t="n">
-        <v>0.8235202844734042</v>
+        <v>2.115613822533694</v>
       </c>
       <c r="E51" t="n">
-        <v>0.8293038487434388</v>
+        <v>-0.8519440770149231</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1580699010153415</v>
+        <v>2.733814552383617</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 6, "learning_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4.871712625026703</v>
+        <v>9.7106072306633</v>
       </c>
       <c r="D52" t="n">
-        <v>0.8220537039552995</v>
+        <v>1.71077082377206</v>
       </c>
       <c r="E52" t="n">
-        <v>0.8293221116065979</v>
+        <v>-0.5279644966125489</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1580560477954412</v>
+        <v>1.9976620285259</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 6, "learning_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4.871712625026703</v>
+        <v>9.842530936002731</v>
       </c>
       <c r="D53" t="n">
-        <v>0.8220537039552995</v>
+        <v>1.609521470667402</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8293221116065979</v>
+        <v>-0.5675844192504883</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1580560477954412</v>
+        <v>2.104281955203725</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KAN</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{"width": [16, 1], "grid_size": 5, "spline_order": 3, "learning_rate": 0.01}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4.917742535471916</v>
+        <v>9.848518520593643</v>
       </c>
       <c r="D54" t="n">
-        <v>0.9213557588577448</v>
+        <v>1.549598104799833</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8311421632766723</v>
+        <v>-0.7813469290733337</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1503146684591974</v>
+        <v>2.529315973548365</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{"degree": 2, "alpha": 1.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4.930507242679596</v>
+        <v>10.02710714936256</v>
       </c>
       <c r="D55" t="n">
-        <v>0.7201447934970013</v>
+        <v>1.894804516463738</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8283694982528687</v>
+        <v>-0.5725799322128295</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1544198758156889</v>
+        <v>1.981502316510068</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 2, "learning_rate": 0.05}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4.94009830443864</v>
+        <v>10.18515810370445</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9769052927234824</v>
+        <v>2.348058508184425</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8425220203308538</v>
+        <v>-0.813540780544281</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1334337543869737</v>
+        <v>2.444120481049772</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{"degree": 3, "alpha": 1.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4.958411902189255</v>
+        <v>10.19541397690773</v>
       </c>
       <c r="D57" t="n">
-        <v>1.352552161346823</v>
+        <v>1.627973342426152</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7997732758522034</v>
+        <v>-1.376514148712158</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1638844923678295</v>
+        <v>3.678352746850014</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 10.0, "epsilon": 0.5, "gamma": "scale"}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4.980977247432351</v>
+        <v>10.28309002518654</v>
       </c>
       <c r="D58" t="n">
-        <v>0.7261092445441243</v>
+        <v>1.83187415696546</v>
       </c>
       <c r="E58" t="n">
-        <v>0.8135937841326684</v>
+        <v>-1.234418618679047</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1510468989304681</v>
+        <v>3.241470043185232</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{"degree": 2, "alpha": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4.981867894530296</v>
+        <v>10.2946113049984</v>
       </c>
       <c r="D59" t="n">
-        <v>0.8204650692932866</v>
+        <v>1.942809748318593</v>
       </c>
       <c r="E59" t="n">
-        <v>0.8279572248458862</v>
+        <v>-1.188597476482391</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1554275517695248</v>
+        <v>3.20859557484542</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 300, "max_depth": -1, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5.030044838786125</v>
+        <v>10.52375862252852</v>
       </c>
       <c r="D60" t="n">
-        <v>0.5699188057410153</v>
+        <v>5.848936206855041</v>
       </c>
       <c r="E60" t="n">
-        <v>0.8217577576637268</v>
+        <v>-0.942035150596972</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1325776839600701</v>
+        <v>2.928856831666993</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 2, "learning_rate": 0.05}</t>
+          <t>{"n_estimators": 300, "max_depth": 10, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5.084710735031891</v>
+        <v>10.52375862252852</v>
       </c>
       <c r="D61" t="n">
-        <v>1.348570974377559</v>
+        <v>5.848936206855041</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8291318730120265</v>
+        <v>-0.942035150596972</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1621775791209516</v>
+        <v>2.928856831666993</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{"degree": 3, "alpha": 0.1}</t>
+          <t>{"n_estimators": 300, "max_depth": 10, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5.090930052101612</v>
+        <v>10.53968916537839</v>
       </c>
       <c r="D62" t="n">
-        <v>1.719912817937795</v>
+        <v>6.000706260355111</v>
       </c>
       <c r="E62" t="n">
-        <v>0.7678247094154358</v>
+        <v>-0.8837437903877247</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1931443120290384</v>
+        <v>2.814783732031616</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 300, "max_depth": -1, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5.169756487011909</v>
+        <v>10.53968916537839</v>
       </c>
       <c r="D63" t="n">
-        <v>0.2988688963154904</v>
+        <v>6.000706260355111</v>
       </c>
       <c r="E63" t="n">
-        <v>0.8220675468444825</v>
+        <v>-0.8837437903877247</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1361022621213229</v>
+        <v>2.814783732031616</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 200, "max_depth": -1, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5.180516317486763</v>
+        <v>10.54640490278907</v>
       </c>
       <c r="D64" t="n">
-        <v>0.6106555616509125</v>
+        <v>5.999607927753765</v>
       </c>
       <c r="E64" t="n">
-        <v>0.809390926361084</v>
+        <v>-0.9226836123638391</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1535694799488645</v>
+        <v>2.889338957225716</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GaussianProcess</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{"length_scale": 1.0, "noise": 0.1, "alpha": 1e-06}</t>
+          <t>{"n_estimators": 200, "max_depth": 10, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5.206212631663956</v>
+        <v>10.54640490278907</v>
       </c>
       <c r="D65" t="n">
-        <v>0.8301408217640737</v>
+        <v>5.999607927753765</v>
       </c>
       <c r="E65" t="n">
-        <v>0.8274209580276499</v>
+        <v>-0.9226836123638391</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1319680407346774</v>
+        <v>2.889338957225716</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GaussianProcess</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{"length_scale": 1.0, "noise": 1.0, "alpha": 1e-06}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5.20621730518334</v>
+        <v>10.57601273059845</v>
       </c>
       <c r="D66" t="n">
-        <v>0.8301435759616076</v>
+        <v>1.406579880966722</v>
       </c>
       <c r="E66" t="n">
-        <v>0.827420792378236</v>
+        <v>-0.7789629101753235</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1319679552576982</v>
+        <v>2.243799375399123</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 200, "max_depth": 10, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5.251635611057281</v>
+        <v>10.61767309481703</v>
       </c>
       <c r="D67" t="n">
-        <v>0.3085381090631436</v>
+        <v>6.054135769868688</v>
       </c>
       <c r="E67" t="n">
-        <v>0.8217396140098572</v>
+        <v>-0.8543648790024237</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1397897777004473</v>
+        <v>2.738561291752066</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 200, "max_depth": -1, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5.263043269515038</v>
+        <v>10.61767309481703</v>
       </c>
       <c r="D68" t="n">
-        <v>1.09791865856608</v>
+        <v>6.054135769868688</v>
       </c>
       <c r="E68" t="n">
-        <v>0.816941785812378</v>
+        <v>-0.8543648790024237</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1292142289713215</v>
+        <v>2.738561291752066</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 100, "max_depth": 10, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5.324565023183823</v>
+        <v>10.62804415863588</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7151312945566866</v>
+        <v>6.104881346201611</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8168110370635986</v>
+        <v>-0.8781856734571425</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1501179422419455</v>
+        <v>2.785905299571086</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 100, "max_depth": -1, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5.339803174138069</v>
+        <v>10.62804415863588</v>
       </c>
       <c r="D70" t="n">
-        <v>1.163833207008714</v>
+        <v>6.104881346201611</v>
       </c>
       <c r="E70" t="n">
-        <v>0.817362928390503</v>
+        <v>-0.8781856734571425</v>
       </c>
       <c r="F70" t="n">
-        <v>0.114496790453923</v>
+        <v>2.785905299571086</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{"degree": 2, "alpha": 10.0}</t>
+          <t>{"n_estimators": 100, "max_depth": 2, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5.364408046007156</v>
+        <v>10.65763621494678</v>
       </c>
       <c r="D71" t="n">
-        <v>1.148183562185765</v>
+        <v>7.75392425776727</v>
       </c>
       <c r="E71" t="n">
-        <v>0.8199068427085876</v>
+        <v>-0.5380728458625521</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1467630219170591</v>
+        <v>2.012538763896268</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 100, "max_depth": 10, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5.385200977325439</v>
+        <v>10.70395632436779</v>
       </c>
       <c r="D72" t="n">
-        <v>0.6140872170894333</v>
+        <v>6.146414739796254</v>
       </c>
       <c r="E72" t="n">
-        <v>0.8078576564788819</v>
+        <v>-0.7412337750959109</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1610499067132831</v>
+        <v>2.489017954247131</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 100, "max_depth": -1, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5.408261343836784</v>
+        <v>10.70395632436779</v>
       </c>
       <c r="D73" t="n">
-        <v>1.143718537825476</v>
+        <v>6.146414739796254</v>
       </c>
       <c r="E73" t="n">
-        <v>0.7960650324821472</v>
+        <v>-0.7412337750959109</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1948753050164627</v>
+        <v>2.489017954247131</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 200, "max_depth": 2, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5.449683964252472</v>
+        <v>10.71514599974106</v>
       </c>
       <c r="D74" t="n">
-        <v>1.022482535801115</v>
+        <v>7.502491468711602</v>
       </c>
       <c r="E74" t="n">
-        <v>0.7846824407577515</v>
+        <v>-0.6550400173134558</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2133245118080189</v>
+        <v>2.254949371332363</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"kernel": "rbf", "C": 100.0, "epsilon": 0.1, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5.450371727347374</v>
+        <v>10.80019328092372</v>
       </c>
       <c r="D75" t="n">
-        <v>1.200323068965804</v>
+        <v>5.452082064318764</v>
       </c>
       <c r="E75" t="n">
-        <v>0.81405588388443</v>
+        <v>-1.15186491395655</v>
       </c>
       <c r="F75" t="n">
-        <v>0.122122961970072</v>
+        <v>3.185215130857772</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"kernel": "rbf", "C": 10.0, "epsilon": 0.1, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5.499716326594353</v>
+        <v>10.89277149116862</v>
       </c>
       <c r="D76" t="n">
-        <v>0.9469411992603882</v>
+        <v>4.930195179830281</v>
       </c>
       <c r="E76" t="n">
-        <v>0.7991051435470581</v>
+        <v>-0.7851771299848302</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1607405198499676</v>
+        <v>2.55306342963094</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"degree": 3, "alpha": 10.0}</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5.60747854411602</v>
+        <v>10.95213711261749</v>
       </c>
       <c r="D77" t="n">
-        <v>0.973496398258889</v>
+        <v>5.671035771155265</v>
       </c>
       <c r="E77" t="n">
-        <v>0.7885964274406433</v>
+        <v>-1.292676901817322</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1999891768523799</v>
+        <v>3.456402057384282</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"kernel": "rbf", "C": 100.0, "epsilon": 0.5, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>5.627202466130257</v>
+        <v>10.98168035256945</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9525315688504901</v>
+        <v>5.175283760925304</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7818383336067199</v>
+        <v>-1.087904271202212</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1831936299374128</v>
+        <v>3.04774212803542</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 100, "max_depth": null, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5.634795799851418</v>
+        <v>11.06281624864909</v>
       </c>
       <c r="D79" t="n">
-        <v>0.7140597124021526</v>
+        <v>6.271551391363723</v>
       </c>
       <c r="E79" t="n">
-        <v>0.7960194706916809</v>
+        <v>-1.084752111482109</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1580053588898889</v>
+        <v>3.072568928454588</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 100, "max_depth": 20, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5.649815201759338</v>
+        <v>11.06281624864909</v>
       </c>
       <c r="D80" t="n">
-        <v>1.282952188429258</v>
+        <v>6.271551391363729</v>
       </c>
       <c r="E80" t="n">
-        <v>0.8124622821807861</v>
+        <v>-1.084752111482109</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1113631483316033</v>
+        <v>3.072568928454587</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 100, "max_depth": 10, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5.704501643776894</v>
+        <v>11.06281624864909</v>
       </c>
       <c r="D81" t="n">
-        <v>0.8047131472238193</v>
+        <v>6.27155139136373</v>
       </c>
       <c r="E81" t="n">
-        <v>0.7824970245361328</v>
+        <v>-1.084752111482109</v>
       </c>
       <c r="F81" t="n">
-        <v>0.219757383039444</v>
+        <v>3.072568928454587</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 100, "max_depth": 10, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5.716593563556671</v>
+        <v>11.06291188363053</v>
       </c>
       <c r="D82" t="n">
-        <v>1.017722275613699</v>
+        <v>6.264727394574492</v>
       </c>
       <c r="E82" t="n">
-        <v>0.7716848731040955</v>
+        <v>-1.081700934713091</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2349182005261947</v>
+        <v>3.077674729460514</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 100, "max_depth": 20, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5.729981511831284</v>
+        <v>11.06291188363054</v>
       </c>
       <c r="D83" t="n">
-        <v>1.218765296478869</v>
+        <v>6.264727394574492</v>
       </c>
       <c r="E83" t="n">
-        <v>0.7806829214096069</v>
+        <v>-1.081700934713091</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2060934392848053</v>
+        <v>3.077674729460513</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 100, "max_depth": null, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5.775860026478767</v>
+        <v>11.06291188363054</v>
       </c>
       <c r="D84" t="n">
-        <v>0.8179184202860316</v>
+        <v>6.264727394574492</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7785289883613586</v>
+        <v>-1.081700934713091</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1900940077303164</v>
+        <v>3.077674729460513</v>
       </c>
     </row>
     <row r="85">
@@ -2460,476 +2460,476 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>5.799980387091637</v>
+        <v>11.14305764436722</v>
       </c>
       <c r="D85" t="n">
-        <v>0.7314228266697793</v>
+        <v>1.751482974199109</v>
       </c>
       <c r="E85" t="n">
-        <v>0.7788089275360107</v>
+        <v>-1.305165100097656</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1741990216833208</v>
+        <v>3.272246188439803</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 300, "max_depth": null, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5.85516631603241</v>
+        <v>11.21735221066398</v>
       </c>
       <c r="D86" t="n">
-        <v>0.8307894895080276</v>
+        <v>6.571757042929044</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7705717444419861</v>
+        <v>-1.039506695857414</v>
       </c>
       <c r="F86" t="n">
-        <v>0.178679505705984</v>
+        <v>2.948404991914163</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 300, "max_depth": 10, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5.890168473124504</v>
+        <v>11.21735221066399</v>
       </c>
       <c r="D87" t="n">
-        <v>0.8917286706188496</v>
+        <v>6.571757042929042</v>
       </c>
       <c r="E87" t="n">
-        <v>0.809599757194519</v>
+        <v>-1.039506695857413</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1137690965294446</v>
+        <v>2.948404991914158</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 300, "max_depth": 20, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5.895354151725769</v>
+        <v>11.21735221066399</v>
       </c>
       <c r="D88" t="n">
-        <v>1.14622269969245</v>
+        <v>6.571757042929047</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7533738017082214</v>
+        <v>-1.039506695857412</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2399105303306557</v>
+        <v>2.948404991914157</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 300, "max_depth": 10, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5.906866267323494</v>
+        <v>11.24454397295825</v>
       </c>
       <c r="D89" t="n">
-        <v>1.067052670907674</v>
+        <v>6.613831411754617</v>
       </c>
       <c r="E89" t="n">
-        <v>0.7474876403808594</v>
+        <v>-1.037182992187834</v>
       </c>
       <c r="F89" t="n">
-        <v>0.2674334542312435</v>
+        <v>2.948688631180043</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 300, "max_depth": 20, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5.964661985635757</v>
+        <v>11.24454397295825</v>
       </c>
       <c r="D90" t="n">
-        <v>0.9054972824613809</v>
+        <v>6.61383141175462</v>
       </c>
       <c r="E90" t="n">
-        <v>0.7596075773239136</v>
+        <v>-1.03718299218783</v>
       </c>
       <c r="F90" t="n">
-        <v>0.2494373658911806</v>
+        <v>2.948688631180036</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 300, "max_depth": null, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5.990587547421455</v>
+        <v>11.24454397295826</v>
       </c>
       <c r="D91" t="n">
-        <v>1.282002474823882</v>
+        <v>6.613831411754624</v>
       </c>
       <c r="E91" t="n">
-        <v>0.7959666728973389</v>
+        <v>-1.037182992187833</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1248114982647448</v>
+        <v>2.94868863118004</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": null, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>6.037441119551659</v>
+        <v>11.32009096667641</v>
       </c>
       <c r="D92" t="n">
-        <v>1.40960936174051</v>
+        <v>6.671628456384511</v>
       </c>
       <c r="E92" t="n">
-        <v>0.7803716778755188</v>
+        <v>-1.10479397973898</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1745610488273315</v>
+        <v>3.074475525548903</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": 10, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6.168215349316597</v>
+        <v>11.32009096667641</v>
       </c>
       <c r="D93" t="n">
-        <v>1.318269775589494</v>
+        <v>6.671628456384514</v>
       </c>
       <c r="E93" t="n">
-        <v>0.7580087780952454</v>
+        <v>-1.104793979738979</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1852792875504565</v>
+        <v>3.0744755255489</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": 20, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6.198985278606415</v>
+        <v>11.32009096667641</v>
       </c>
       <c r="D94" t="n">
-        <v>0.9156044244310665</v>
+        <v>6.671628456384512</v>
       </c>
       <c r="E94" t="n">
-        <v>0.7748417496681214</v>
+        <v>-1.104793979738981</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1416243539897337</v>
+        <v>3.074475525548904</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": 20, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>6.218664646148682</v>
+        <v>11.32333396439832</v>
       </c>
       <c r="D95" t="n">
-        <v>0.8401405042579183</v>
+        <v>6.675509309975749</v>
       </c>
       <c r="E95" t="n">
-        <v>0.7516100525856018</v>
+        <v>-1.109451224887761</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1890717087564248</v>
+        <v>3.074505981412141</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": 10, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6.221040636301041</v>
+        <v>11.32333396439832</v>
       </c>
       <c r="D96" t="n">
-        <v>0.5149650065747278</v>
+        <v>6.675509309975749</v>
       </c>
       <c r="E96" t="n">
-        <v>0.7543053865432739</v>
+        <v>-1.109451224887762</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1833333488875037</v>
+        <v>3.074505981412143</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": null, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6.243505477905273</v>
+        <v>11.32333396439832</v>
       </c>
       <c r="D97" t="n">
-        <v>1.136431244384331</v>
+        <v>6.675509309975744</v>
       </c>
       <c r="E97" t="n">
-        <v>0.7496274948120117</v>
+        <v>-1.109451224887763</v>
       </c>
       <c r="F97" t="n">
-        <v>0.1937451090658439</v>
+        <v>3.074505981412146</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"kernel": "rbf", "C": 10.0, "epsilon": 0.5, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6.519312486052513</v>
+        <v>11.34216056588669</v>
       </c>
       <c r="D98" t="n">
-        <v>0.9831672458224766</v>
+        <v>4.726151912188235</v>
       </c>
       <c r="E98" t="n">
-        <v>0.7308651685714722</v>
+        <v>-0.8889277748114903</v>
       </c>
       <c r="F98" t="n">
-        <v>0.2046328555596468</v>
+        <v>2.681464227228796</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6.693485230207443</v>
+        <v>11.8433864980438</v>
       </c>
       <c r="D99" t="n">
-        <v>0.8753123905406748</v>
+        <v>7.874478892293797</v>
       </c>
       <c r="E99" t="n">
-        <v>0.7025119185447692</v>
+        <v>-1.018918645894489</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2934106060903186</v>
+        <v>2.746217388409948</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>6.741749048233032</v>
+        <v>11.91210852637836</v>
       </c>
       <c r="D100" t="n">
-        <v>1.138956746525674</v>
+        <v>7.948943226306748</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7093704462051391</v>
+        <v>-1.086639765575006</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1798054577525373</v>
+        <v>2.855559739788269</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"degree": 3, "alpha": 1.0}</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7.005861699581146</v>
+        <v>12.09095790982246</v>
       </c>
       <c r="D101" t="n">
-        <v>1.066913785038853</v>
+        <v>5.545427414842034</v>
       </c>
       <c r="E101" t="n">
-        <v>0.7118112206459045</v>
+        <v>-2.361207342147827</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2225529453804251</v>
+        <v>5.322372234819952</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 1.0, "epsilon": 0.1, "gamma": "scale"}</t>
+          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>7.056498456436444</v>
+        <v>12.2708861850442</v>
       </c>
       <c r="D102" t="n">
-        <v>2.355528662327718</v>
+        <v>8.887375850987764</v>
       </c>
       <c r="E102" t="n">
-        <v>0.7666134359524789</v>
+        <v>-0.9909388405969846</v>
       </c>
       <c r="F102" t="n">
-        <v>0.09864567482091498</v>
+        <v>2.588127505555807</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>7.13845856487751</v>
+        <v>12.4096002146386</v>
       </c>
       <c r="D103" t="n">
-        <v>1.399473106160495</v>
+        <v>9.036731193152479</v>
       </c>
       <c r="E103" t="n">
-        <v>0.6319970250129699</v>
+        <v>-1.094543225492989</v>
       </c>
       <c r="F103" t="n">
-        <v>0.4054397450417821</v>
+        <v>2.751962785977415</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"kernel": "rbf", "C": 1.0, "epsilon": 0.5, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>7.156457304954529</v>
+        <v>12.4405114964409</v>
       </c>
       <c r="D104" t="n">
-        <v>1.306261845558522</v>
+        <v>6.267269028200894</v>
       </c>
       <c r="E104" t="n">
-        <v>0.7321543335914612</v>
+        <v>-1.470626517179303</v>
       </c>
       <c r="F104" t="n">
-        <v>0.1546799148750552</v>
+        <v>3.639488312898562</v>
       </c>
     </row>
     <row r="105">
@@ -2940,68 +2940,68 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 1.0, "epsilon": 0.5, "gamma": "scale"}</t>
+          <t>{"kernel": "rbf", "C": 1.0, "epsilon": 0.1, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>7.251889295286134</v>
+        <v>12.5604165547405</v>
       </c>
       <c r="D105" t="n">
-        <v>2.35298843411249</v>
+        <v>5.961389665173265</v>
       </c>
       <c r="E105" t="n">
-        <v>0.757815784473732</v>
+        <v>-1.605845355362209</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1048718464530129</v>
+        <v>3.894046169590094</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"degree": 2, "alpha": 0.1}</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>7.444863617420197</v>
+        <v>12.58723065257072</v>
       </c>
       <c r="D106" t="n">
-        <v>0.5965616871242526</v>
+        <v>11.22277924051722</v>
       </c>
       <c r="E106" t="n">
-        <v>0.652360987663269</v>
+        <v>-1.271607983112335</v>
       </c>
       <c r="F106" t="n">
-        <v>0.291794024859569</v>
+        <v>3.007984651642118</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"degree": 3, "alpha": 0.1}</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>7.676726207137108</v>
+        <v>12.85960547626019</v>
       </c>
       <c r="D107" t="n">
-        <v>1.159960836172227</v>
+        <v>5.901041594960271</v>
       </c>
       <c r="E107" t="n">
-        <v>0.6562538027763367</v>
+        <v>-2.999195230007172</v>
       </c>
       <c r="F107" t="n">
-        <v>0.2816904916515438</v>
+        <v>6.404197319140013</v>
       </c>
     </row>
     <row r="108">
@@ -3016,16 +3016,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>13.0100355297327</v>
+        <v>17.18860372900963</v>
       </c>
       <c r="D108" t="n">
-        <v>7.772000813461913</v>
+        <v>8.233551896023172</v>
       </c>
       <c r="E108" t="n">
-        <v>0.003199601173400879</v>
+        <v>-5.426932191848755</v>
       </c>
       <c r="F108" t="n">
-        <v>0.9308203929563703</v>
+        <v>10.67137766278031</v>
       </c>
     </row>
     <row r="109">
@@ -3036,20 +3036,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>15.24001777172089</v>
+        <v>17.23955288529396</v>
       </c>
       <c r="D109" t="n">
-        <v>7.400350787638883</v>
+        <v>8.131652819870324</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.1628199338912964</v>
+        <v>-5.41562077999115</v>
       </c>
       <c r="F109" t="n">
-        <v>0.8390368933908873</v>
+        <v>10.66179200572855</v>
       </c>
     </row>
     <row r="110">
@@ -3060,20 +3060,20 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>17.86150738596916</v>
+        <v>17.35401943325996</v>
       </c>
       <c r="D110" t="n">
-        <v>3.879324880890826</v>
+        <v>7.976591336839622</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.3846537351608276</v>
+        <v>-5.465903425216675</v>
       </c>
       <c r="F110" t="n">
-        <v>0.637189469632072</v>
+        <v>10.7022298435603</v>
       </c>
     </row>
     <row r="111">
@@ -3084,20 +3084,20 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>17.86970168352127</v>
+        <v>18.29918950796127</v>
       </c>
       <c r="D111" t="n">
-        <v>3.855841043545217</v>
+        <v>6.987982159136772</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.3876621246337891</v>
+        <v>-5.569554424285888</v>
       </c>
       <c r="F111" t="n">
-        <v>0.6441275449746704</v>
+        <v>10.58795737482569</v>
       </c>
     </row>
     <row r="112">
@@ -3108,20 +3108,20 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>17.87638887763023</v>
+        <v>18.30623969435692</v>
       </c>
       <c r="D112" t="n">
-        <v>3.87051551757045</v>
+        <v>7.030678089499679</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.3846049070358276</v>
+        <v>-5.556888079643249</v>
       </c>
       <c r="F112" t="n">
-        <v>0.6453083578177513</v>
+        <v>10.55514960672071</v>
       </c>
     </row>
     <row r="113">
@@ -3132,20 +3132,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>17.91628882288933</v>
+        <v>18.30971717834473</v>
       </c>
       <c r="D113" t="n">
-        <v>3.950985813769869</v>
+        <v>7.013897107550881</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.376203203201294</v>
+        <v>-5.573478150367737</v>
       </c>
       <c r="F113" t="n">
-        <v>0.6464124904480831</v>
+        <v>10.59082280931892</v>
       </c>
     </row>
     <row r="114">
@@ -3160,16 +3160,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>17.9220025241375</v>
+        <v>18.31197530031204</v>
       </c>
       <c r="D114" t="n">
-        <v>3.969094870464817</v>
+        <v>7.022336989938021</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.3747264862060547</v>
+        <v>-5.558951497077942</v>
       </c>
       <c r="F114" t="n">
-        <v>0.6445279416556751</v>
+        <v>10.55984028950115</v>
       </c>
     </row>
     <row r="115">
@@ -3180,20 +3180,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>17.92684331536293</v>
+        <v>18.3784893155098</v>
       </c>
       <c r="D115" t="n">
-        <v>3.979488268726511</v>
+        <v>7.011115141839738</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.3725012540817261</v>
+        <v>-5.577347135543823</v>
       </c>
       <c r="F115" t="n">
-        <v>0.6472104136118103</v>
+        <v>10.57748395040206</v>
       </c>
     </row>
     <row r="116">
@@ -3204,20 +3204,20 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>17.98869907855988</v>
+        <v>18.38845387101173</v>
       </c>
       <c r="D116" t="n">
-        <v>4.290402076441463</v>
+        <v>7.019450114568567</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.3544872045516968</v>
+        <v>-5.578357219696045</v>
       </c>
       <c r="F116" t="n">
-        <v>0.6599885458312995</v>
+        <v>10.5776714808141</v>
       </c>
     </row>
     <row r="117">
@@ -3228,20 +3228,20 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>18.01492422819138</v>
+        <v>18.39205324649811</v>
       </c>
       <c r="D117" t="n">
-        <v>4.406625535085658</v>
+        <v>7.007095725833745</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.3516219854354858</v>
+        <v>-5.572254025936127</v>
       </c>
       <c r="F117" t="n">
-        <v>0.6509665261745853</v>
+        <v>10.56483116188875</v>
       </c>
     </row>
   </sheetData>
